--- a/DATA/RAW/Clientes.xlsx
+++ b/DATA/RAW/Clientes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="1" r:id="R00dc268f811c4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="1" r:id="R5add93a1bb5b465a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45,34 +45,25 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaClientes" displayName="TablaClientes" ref="A1:D251" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="IDCliente"/>
-    <x:tableColumn id="2" name="TipoDocumento"/>
-    <x:tableColumn id="3" name="NombreRazonSocial"/>
-    <x:tableColumn id="4" name="TipoCliente"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -276,29 +267,29 @@
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>IDCliente</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>TipoDocumento</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>NombreRazonSocial</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>TipoCliente</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>70000001</x:v>
+        <x:v>90000104</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Cliente Persona 001</x:v>
+        <x:v>Christian García García</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>Persona</x:v>
@@ -306,13 +297,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>70000002</x:v>
+        <x:v>90000173</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Cliente Persona 002</x:v>
+        <x:v>Jorge Reyes López</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Persona</x:v>
@@ -320,13 +311,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>70000003</x:v>
+        <x:v>90000157</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Cliente Persona 003</x:v>
+        <x:v>Rosa Medina Flores</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Persona</x:v>
@@ -334,27 +325,27 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>70000004</x:v>
+        <x:v>20990000019</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Cliente Persona 004</x:v>
+        <x:v>Negocios Continental 19 S.A.C.</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>70000005</x:v>
+        <x:v>90000053</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Cliente Persona 005</x:v>
+        <x:v>Daniela Vargas Silva</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>Persona</x:v>
@@ -362,27 +353,27 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>70000006</x:v>
+        <x:v>20990000044</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Cliente Persona 006</x:v>
+        <x:v>Grupo Comercial Horizonte 44 S.A.C.</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>70000007</x:v>
+        <x:v>90000111</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Cliente Persona 007</x:v>
+        <x:v>Valeria Chávez Valdez</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>Persona</x:v>
@@ -390,13 +381,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>70000008</x:v>
+        <x:v>90000129</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Cliente Persona 008</x:v>
+        <x:v>Fiorella Paredes Cárdenas</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>Persona</x:v>
@@ -404,13 +395,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>70000009</x:v>
+        <x:v>90000063</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>Cliente Persona 009</x:v>
+        <x:v>Alejandra Aguilar Chávez</x:v>
       </x:c>
       <x:c r="D10" t="str">
         <x:v>Persona</x:v>
@@ -418,27 +409,27 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>70000010</x:v>
+        <x:v>20990000037</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Cliente Persona 010</x:v>
+        <x:v>Grupo Comercial Santa Rosa 37 S.R.L.</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>70000011</x:v>
+        <x:v>90000089</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Cliente Persona 011</x:v>
+        <x:v>Eduardo Valdez Ramírez</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>Persona</x:v>
@@ -446,13 +437,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>70000012</x:v>
+        <x:v>90000036</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Cliente Persona 012</x:v>
+        <x:v>Claudia Campos Vargas</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>Persona</x:v>
@@ -460,27 +451,27 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>70000013</x:v>
+        <x:v>20990000049</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Cliente Persona 013</x:v>
+        <x:v>Representaciones Continental 49 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>70000014</x:v>
+        <x:v>90000034</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Cliente Persona 014</x:v>
+        <x:v>Ricardo Campos Cárdenas</x:v>
       </x:c>
       <x:c r="D15" t="str">
         <x:v>Persona</x:v>
@@ -488,13 +479,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>70000015</x:v>
+        <x:v>90000017</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Cliente Persona 015</x:v>
+        <x:v>Luis García Campos</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>Persona</x:v>
@@ -502,13 +493,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>70000016</x:v>
+        <x:v>90000138</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Cliente Persona 016</x:v>
+        <x:v>José Salazar Sánchez</x:v>
       </x:c>
       <x:c r="D17" t="str">
         <x:v>Persona</x:v>
@@ -516,13 +507,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>70000017</x:v>
+        <x:v>90000008</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Cliente Persona 017</x:v>
+        <x:v>María Castillo Navarro</x:v>
       </x:c>
       <x:c r="D18" t="str">
         <x:v>Persona</x:v>
@@ -530,13 +521,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>70000018</x:v>
+        <x:v>90000006</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Cliente Persona 018</x:v>
+        <x:v>Carlos Herrera García</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>Persona</x:v>
@@ -544,13 +535,13 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>70000019</x:v>
+        <x:v>90000011</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Cliente Persona 019</x:v>
+        <x:v>Martín Quispe Campos</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>Persona</x:v>
@@ -558,13 +549,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>70000020</x:v>
+        <x:v>90000132</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Cliente Persona 020</x:v>
+        <x:v>María Fernández Sánchez</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>Persona</x:v>
@@ -572,27 +563,27 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>70000021</x:v>
+        <x:v>20990000028</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Cliente Persona 021</x:v>
+        <x:v>Distribuidora Futura 28 S.A.C.</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>70000022</x:v>
+        <x:v>90000064</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Cliente Persona 022</x:v>
+        <x:v>Patricia Sánchez Sánchez</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>Persona</x:v>
@@ -600,13 +591,13 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>70000023</x:v>
+        <x:v>90000071</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Cliente Persona 023</x:v>
+        <x:v>Patricia Torres Cárdenas</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>Persona</x:v>
@@ -614,27 +605,27 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>70000024</x:v>
+        <x:v>20990000064</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Cliente Persona 024</x:v>
+        <x:v>Corporación San Marcos 64 S.R.L.</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>70000025</x:v>
+        <x:v>90000137</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Cliente Persona 025</x:v>
+        <x:v>Alejandra López García</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>Persona</x:v>
@@ -642,41 +633,41 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>70000026</x:v>
+        <x:v>20990000012</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Cliente Persona 026</x:v>
+        <x:v>Inversiones Progreso 12 S.R.L.</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>70000027</x:v>
+        <x:v>20990000047</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Cliente Persona 027</x:v>
+        <x:v>Servicios Generales Horizonte 47 S.R.L.</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>70000028</x:v>
+        <x:v>90000043</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Cliente Persona 028</x:v>
+        <x:v>Ricardo García Chávez</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>Persona</x:v>
@@ -684,27 +675,27 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>70000029</x:v>
+        <x:v>20990000016</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Cliente Persona 029</x:v>
+        <x:v>Representaciones Futura 16 S.R.L.</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>70000030</x:v>
+        <x:v>90000122</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Cliente Persona 030</x:v>
+        <x:v>Ricardo Espinoza Espinoza</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>Persona</x:v>
@@ -712,27 +703,27 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>70000031</x:v>
+        <x:v>20990000025</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>Cliente Persona 031</x:v>
+        <x:v>Distribuidora Lima Norte 25 S.R.L.</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>70000032</x:v>
+        <x:v>90000026</x:v>
       </x:c>
       <x:c r="B33" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>Cliente Persona 032</x:v>
+        <x:v>Miguel Torres García</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>Persona</x:v>
@@ -740,27 +731,27 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>70000033</x:v>
+        <x:v>20990000043</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>Cliente Persona 033</x:v>
+        <x:v>Inversiones Los Cedros 43 S.R.L.</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>70000034</x:v>
+        <x:v>90000038</x:v>
       </x:c>
       <x:c r="B35" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Cliente Persona 034</x:v>
+        <x:v>Sofía López Reyes</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>Persona</x:v>
@@ -768,13 +759,13 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>70000035</x:v>
+        <x:v>90000107</x:v>
       </x:c>
       <x:c r="B36" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>Cliente Persona 035</x:v>
+        <x:v>Álvaro Aguilar Paredes</x:v>
       </x:c>
       <x:c r="D36" t="str">
         <x:v>Persona</x:v>
@@ -782,13 +773,13 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>70000036</x:v>
+        <x:v>90000060</x:v>
       </x:c>
       <x:c r="B37" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Cliente Persona 036</x:v>
+        <x:v>Eduardo Gutiérrez Cueva</x:v>
       </x:c>
       <x:c r="D37" t="str">
         <x:v>Persona</x:v>
@@ -796,13 +787,13 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>70000037</x:v>
+        <x:v>90000172</x:v>
       </x:c>
       <x:c r="B38" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Cliente Persona 037</x:v>
+        <x:v>Martín Torres Valdez</x:v>
       </x:c>
       <x:c r="D38" t="str">
         <x:v>Persona</x:v>
@@ -810,13 +801,13 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>70000038</x:v>
+        <x:v>90000049</x:v>
       </x:c>
       <x:c r="B39" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Cliente Persona 038</x:v>
+        <x:v>Alejandra Castillo Torres</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>Persona</x:v>
@@ -824,27 +815,27 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>70000039</x:v>
+        <x:v>20990000030</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>Cliente Persona 039</x:v>
+        <x:v>Inversiones Progreso 30 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>70000040</x:v>
+        <x:v>90000102</x:v>
       </x:c>
       <x:c r="B41" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Cliente Persona 040</x:v>
+        <x:v>Gabriela Vargas García</x:v>
       </x:c>
       <x:c r="D41" t="str">
         <x:v>Persona</x:v>
@@ -852,27 +843,27 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>70000041</x:v>
+        <x:v>20990000062</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>Cliente Persona 041</x:v>
+        <x:v>Corporación Central 62 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>70000042</x:v>
+        <x:v>90000180</x:v>
       </x:c>
       <x:c r="B43" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Cliente Persona 042</x:v>
+        <x:v>Carlos Rodríguez Valdez</x:v>
       </x:c>
       <x:c r="D43" t="str">
         <x:v>Persona</x:v>
@@ -880,13 +871,13 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>70000043</x:v>
+        <x:v>90000098</x:v>
       </x:c>
       <x:c r="B44" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>Cliente Persona 043</x:v>
+        <x:v>Jorge Campos Silva</x:v>
       </x:c>
       <x:c r="D44" t="str">
         <x:v>Persona</x:v>
@@ -894,27 +885,27 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>70000044</x:v>
+        <x:v>20990000006</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>Cliente Persona 044</x:v>
+        <x:v>Suministros Horizonte 06 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>70000045</x:v>
+        <x:v>90000059</x:v>
       </x:c>
       <x:c r="B46" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>Cliente Persona 045</x:v>
+        <x:v>Marco Rodríguez Rodríguez</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>Persona</x:v>
@@ -922,13 +913,13 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>70000046</x:v>
+        <x:v>90000158</x:v>
       </x:c>
       <x:c r="B47" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>Cliente Persona 046</x:v>
+        <x:v>Valeria Torres Paredes</x:v>
       </x:c>
       <x:c r="D47" t="str">
         <x:v>Persona</x:v>
@@ -936,13 +927,13 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>70000047</x:v>
+        <x:v>90000153</x:v>
       </x:c>
       <x:c r="B48" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>Cliente Persona 047</x:v>
+        <x:v>Camila Navarro Aguilar</x:v>
       </x:c>
       <x:c r="D48" t="str">
         <x:v>Persona</x:v>
@@ -950,13 +941,13 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>70000048</x:v>
+        <x:v>90000118</x:v>
       </x:c>
       <x:c r="B49" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>Cliente Persona 048</x:v>
+        <x:v>Fernando Cueva Silva</x:v>
       </x:c>
       <x:c r="D49" t="str">
         <x:v>Persona</x:v>
@@ -964,27 +955,27 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>70000049</x:v>
+        <x:v>20990000010</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Cliente Persona 049</x:v>
+        <x:v>Suministros Victoria 10 S.R.L.</x:v>
       </x:c>
       <x:c r="D50" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>70000050</x:v>
+        <x:v>90000076</x:v>
       </x:c>
       <x:c r="B51" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Cliente Persona 050</x:v>
+        <x:v>Miguel Torres Navarro</x:v>
       </x:c>
       <x:c r="D51" t="str">
         <x:v>Persona</x:v>
@@ -992,13 +983,13 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>70000051</x:v>
+        <x:v>90000171</x:v>
       </x:c>
       <x:c r="B52" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Cliente Persona 051</x:v>
+        <x:v>Christian Salazar Valdez</x:v>
       </x:c>
       <x:c r="D52" t="str">
         <x:v>Persona</x:v>
@@ -1006,13 +997,13 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>70000052</x:v>
+        <x:v>90000179</x:v>
       </x:c>
       <x:c r="B53" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>Cliente Persona 052</x:v>
+        <x:v>Miguel Quispe Cárdenas</x:v>
       </x:c>
       <x:c r="D53" t="str">
         <x:v>Persona</x:v>
@@ -1020,13 +1011,13 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>70000053</x:v>
+        <x:v>90000057</x:v>
       </x:c>
       <x:c r="B54" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Cliente Persona 053</x:v>
+        <x:v>Patricia Aguilar Cueva</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>Persona</x:v>
@@ -1034,13 +1025,13 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>70000054</x:v>
+        <x:v>90000174</x:v>
       </x:c>
       <x:c r="B55" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>Cliente Persona 054</x:v>
+        <x:v>Lucía Sánchez Rodríguez</x:v>
       </x:c>
       <x:c r="D55" t="str">
         <x:v>Persona</x:v>
@@ -1048,13 +1039,13 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>70000055</x:v>
+        <x:v>90000020</x:v>
       </x:c>
       <x:c r="B56" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>Cliente Persona 055</x:v>
+        <x:v>Rosa Espinoza García</x:v>
       </x:c>
       <x:c r="D56" t="str">
         <x:v>Persona</x:v>
@@ -1062,13 +1053,13 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>70000056</x:v>
+        <x:v>90000147</x:v>
       </x:c>
       <x:c r="B57" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>Cliente Persona 056</x:v>
+        <x:v>Claudia Reyes Reyes</x:v>
       </x:c>
       <x:c r="D57" t="str">
         <x:v>Persona</x:v>
@@ -1076,13 +1067,13 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>70000057</x:v>
+        <x:v>90000161</x:v>
       </x:c>
       <x:c r="B58" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>Cliente Persona 057</x:v>
+        <x:v>Christian Medina Navarro</x:v>
       </x:c>
       <x:c r="D58" t="str">
         <x:v>Persona</x:v>
@@ -1090,13 +1081,13 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>70000058</x:v>
+        <x:v>90000115</x:v>
       </x:c>
       <x:c r="B59" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>Cliente Persona 058</x:v>
+        <x:v>Rosa Paredes Quispe</x:v>
       </x:c>
       <x:c r="D59" t="str">
         <x:v>Persona</x:v>
@@ -1104,41 +1095,41 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>70000059</x:v>
+        <x:v>20990000001</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>Cliente Persona 059</x:v>
+        <x:v>Representaciones Atenea 01 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D60" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>70000060</x:v>
+        <x:v>20990000029</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>Cliente Persona 060</x:v>
+        <x:v>Importaciones San Marcos 29 S.A.C.</x:v>
       </x:c>
       <x:c r="D61" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>70000061</x:v>
+        <x:v>90000041</x:v>
       </x:c>
       <x:c r="B62" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>Cliente Persona 061</x:v>
+        <x:v>Fiorella Navarro Reyes</x:v>
       </x:c>
       <x:c r="D62" t="str">
         <x:v>Persona</x:v>
@@ -1146,13 +1137,13 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>70000062</x:v>
+        <x:v>90000056</x:v>
       </x:c>
       <x:c r="B63" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>Cliente Persona 062</x:v>
+        <x:v>Sofía Rojas García</x:v>
       </x:c>
       <x:c r="D63" t="str">
         <x:v>Persona</x:v>
@@ -1160,13 +1151,13 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>70000063</x:v>
+        <x:v>90000002</x:v>
       </x:c>
       <x:c r="B64" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>Cliente Persona 063</x:v>
+        <x:v>Renzo Flores Silva</x:v>
       </x:c>
       <x:c r="D64" t="str">
         <x:v>Persona</x:v>
@@ -1174,27 +1165,27 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>70000064</x:v>
+        <x:v>20990000004</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>Cliente Persona 064</x:v>
+        <x:v>Inversiones Continental 04 S.A.C.</x:v>
       </x:c>
       <x:c r="D65" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>70000065</x:v>
+        <x:v>90000050</x:v>
       </x:c>
       <x:c r="B66" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>Cliente Persona 065</x:v>
+        <x:v>Alejandra Gutiérrez Mendoza</x:v>
       </x:c>
       <x:c r="D66" t="str">
         <x:v>Persona</x:v>
@@ -1202,13 +1193,13 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>70000066</x:v>
+        <x:v>90000042</x:v>
       </x:c>
       <x:c r="B67" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>Cliente Persona 066</x:v>
+        <x:v>Renzo Cueva Cárdenas</x:v>
       </x:c>
       <x:c r="D67" t="str">
         <x:v>Persona</x:v>
@@ -1216,13 +1207,13 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>70000067</x:v>
+        <x:v>90000131</x:v>
       </x:c>
       <x:c r="B68" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>Cliente Persona 067</x:v>
+        <x:v>Andrea Paredes Vargas</x:v>
       </x:c>
       <x:c r="D68" t="str">
         <x:v>Persona</x:v>
@@ -1230,13 +1221,13 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>70000068</x:v>
+        <x:v>90000039</x:v>
       </x:c>
       <x:c r="B69" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>Cliente Persona 068</x:v>
+        <x:v>Eduardo Mendoza Torres</x:v>
       </x:c>
       <x:c r="D69" t="str">
         <x:v>Persona</x:v>
@@ -1244,13 +1235,13 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>70000069</x:v>
+        <x:v>90000108</x:v>
       </x:c>
       <x:c r="B70" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Cliente Persona 069</x:v>
+        <x:v>Eduardo Ramírez Sánchez</x:v>
       </x:c>
       <x:c r="D70" t="str">
         <x:v>Persona</x:v>
@@ -1258,13 +1249,13 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>70000070</x:v>
+        <x:v>90000081</x:v>
       </x:c>
       <x:c r="B71" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>Cliente Persona 070</x:v>
+        <x:v>Marco Silva López</x:v>
       </x:c>
       <x:c r="D71" t="str">
         <x:v>Persona</x:v>
@@ -1272,13 +1263,13 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>70000071</x:v>
+        <x:v>90000159</x:v>
       </x:c>
       <x:c r="B72" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>Cliente Persona 071</x:v>
+        <x:v>Camila García Sánchez</x:v>
       </x:c>
       <x:c r="D72" t="str">
         <x:v>Persona</x:v>
@@ -1286,13 +1277,13 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>70000072</x:v>
+        <x:v>90000133</x:v>
       </x:c>
       <x:c r="B73" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>Cliente Persona 072</x:v>
+        <x:v>José Flores Fernández</x:v>
       </x:c>
       <x:c r="D73" t="str">
         <x:v>Persona</x:v>
@@ -1300,13 +1291,13 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>70000073</x:v>
+        <x:v>90000066</x:v>
       </x:c>
       <x:c r="B74" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>Cliente Persona 073</x:v>
+        <x:v>José Fernández Silva</x:v>
       </x:c>
       <x:c r="D74" t="str">
         <x:v>Persona</x:v>
@@ -1314,27 +1305,27 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>70000074</x:v>
+        <x:v>20990000058</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>Cliente Persona 074</x:v>
+        <x:v>Inversiones Universal 58 S.A.C.</x:v>
       </x:c>
       <x:c r="D75" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>70000075</x:v>
+        <x:v>90000090</x:v>
       </x:c>
       <x:c r="B76" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>Cliente Persona 075</x:v>
+        <x:v>Claudia Quispe Quispe</x:v>
       </x:c>
       <x:c r="D76" t="str">
         <x:v>Persona</x:v>
@@ -1342,13 +1333,13 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>70000076</x:v>
+        <x:v>90000001</x:v>
       </x:c>
       <x:c r="B77" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>Cliente Persona 076</x:v>
+        <x:v>Gabriela Torres Silva</x:v>
       </x:c>
       <x:c r="D77" t="str">
         <x:v>Persona</x:v>
@@ -1356,13 +1347,13 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>70000077</x:v>
+        <x:v>90000149</x:v>
       </x:c>
       <x:c r="B78" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C78" t="str">
-        <x:v>Cliente Persona 077</x:v>
+        <x:v>Lucía Paredes Gutiérrez</x:v>
       </x:c>
       <x:c r="D78" t="str">
         <x:v>Persona</x:v>
@@ -1370,27 +1361,27 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>70000078</x:v>
+        <x:v>20990000050</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>Cliente Persona 078</x:v>
+        <x:v>Negocios San Marcos 50 S.A.C.</x:v>
       </x:c>
       <x:c r="D79" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>70000079</x:v>
+        <x:v>90000100</x:v>
       </x:c>
       <x:c r="B80" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>Cliente Persona 079</x:v>
+        <x:v>Gabriela Torres Castillo</x:v>
       </x:c>
       <x:c r="D80" t="str">
         <x:v>Persona</x:v>
@@ -1398,27 +1389,27 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>70000080</x:v>
+        <x:v>20990000046</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>Cliente Persona 080</x:v>
+        <x:v>Importaciones Horizonte 46 S.R.L.</x:v>
       </x:c>
       <x:c r="D81" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
-        <x:v>70000081</x:v>
+        <x:v>90000024</x:v>
       </x:c>
       <x:c r="B82" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>Cliente Persona 081</x:v>
+        <x:v>Diego Herrera Navarro</x:v>
       </x:c>
       <x:c r="D82" t="str">
         <x:v>Persona</x:v>
@@ -1426,13 +1417,13 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
-        <x:v>70000082</x:v>
+        <x:v>90000175</x:v>
       </x:c>
       <x:c r="B83" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>Cliente Persona 082</x:v>
+        <x:v>Sofía Ramírez Mendoza</x:v>
       </x:c>
       <x:c r="D83" t="str">
         <x:v>Persona</x:v>
@@ -1440,55 +1431,55 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
-        <x:v>70000083</x:v>
+        <x:v>20990000066</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>Cliente Persona 083</x:v>
+        <x:v>Corporación Atenea 66 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D84" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>70000084</x:v>
+        <x:v>20990000020</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>Cliente Persona 084</x:v>
+        <x:v>Distribuidora Futura 20 S.R.L.</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>70000085</x:v>
+        <x:v>20990000052</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>Cliente Persona 085</x:v>
+        <x:v>Representaciones Santa Rosa 52 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>70000086</x:v>
+        <x:v>90000019</x:v>
       </x:c>
       <x:c r="B87" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>Cliente Persona 086</x:v>
+        <x:v>Daniela Espinoza Rojas</x:v>
       </x:c>
       <x:c r="D87" t="str">
         <x:v>Persona</x:v>
@@ -1496,27 +1487,27 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>70000087</x:v>
+        <x:v>20990000055</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>Cliente Persona 087</x:v>
+        <x:v>Corporación Prisma 55 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>70000088</x:v>
+        <x:v>90000123</x:v>
       </x:c>
       <x:c r="B89" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>Cliente Persona 088</x:v>
+        <x:v>Lucía Medina Vega</x:v>
       </x:c>
       <x:c r="D89" t="str">
         <x:v>Persona</x:v>
@@ -1524,13 +1515,13 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>70000089</x:v>
+        <x:v>90000127</x:v>
       </x:c>
       <x:c r="B90" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>Cliente Persona 089</x:v>
+        <x:v>Fiorella Quispe Cueva</x:v>
       </x:c>
       <x:c r="D90" t="str">
         <x:v>Persona</x:v>
@@ -1538,13 +1529,13 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>70000090</x:v>
+        <x:v>90000168</x:v>
       </x:c>
       <x:c r="B91" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>Cliente Persona 090</x:v>
+        <x:v>Marco Rodríguez Cueva</x:v>
       </x:c>
       <x:c r="D91" t="str">
         <x:v>Persona</x:v>
@@ -1552,13 +1543,13 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>70000091</x:v>
+        <x:v>90000178</x:v>
       </x:c>
       <x:c r="B92" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>Cliente Persona 091</x:v>
+        <x:v>Diego Torres Espinoza</x:v>
       </x:c>
       <x:c r="D92" t="str">
         <x:v>Persona</x:v>
@@ -1566,13 +1557,13 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>70000092</x:v>
+        <x:v>90000021</x:v>
       </x:c>
       <x:c r="B93" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>Cliente Persona 092</x:v>
+        <x:v>Eduardo Quispe Chávez</x:v>
       </x:c>
       <x:c r="D93" t="str">
         <x:v>Persona</x:v>
@@ -1580,69 +1571,69 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>70000093</x:v>
+        <x:v>20990000009</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>Cliente Persona 093</x:v>
+        <x:v>Distribuidora Central 09 S.R.L.</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>70000094</x:v>
+        <x:v>20990000033</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>Cliente Persona 094</x:v>
+        <x:v>Comercial Progreso 33 S.R.L.</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>70000095</x:v>
+        <x:v>20990000021</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>Cliente Persona 095</x:v>
+        <x:v>Corporación Santa Rosa 21 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>70000096</x:v>
+        <x:v>20990000015</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>Cliente Persona 096</x:v>
+        <x:v>Negocios El Dorado 15 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="str">
-        <x:v>70000097</x:v>
+        <x:v>90000134</x:v>
       </x:c>
       <x:c r="B98" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>Cliente Persona 097</x:v>
+        <x:v>Carlos Valdez Aguilar</x:v>
       </x:c>
       <x:c r="D98" t="str">
         <x:v>Persona</x:v>
@@ -1650,13 +1641,13 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="str">
-        <x:v>70000098</x:v>
+        <x:v>90000033</x:v>
       </x:c>
       <x:c r="B99" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>Cliente Persona 098</x:v>
+        <x:v>Diego Campos Ramírez</x:v>
       </x:c>
       <x:c r="D99" t="str">
         <x:v>Persona</x:v>
@@ -1664,13 +1655,13 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>70000099</x:v>
+        <x:v>90000154</x:v>
       </x:c>
       <x:c r="B100" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>Cliente Persona 099</x:v>
+        <x:v>Camila Medina Huamán</x:v>
       </x:c>
       <x:c r="D100" t="str">
         <x:v>Persona</x:v>
@@ -1678,13 +1669,13 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="str">
-        <x:v>70000100</x:v>
+        <x:v>90000013</x:v>
       </x:c>
       <x:c r="B101" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>Cliente Persona 100</x:v>
+        <x:v>María Rojas Espinoza</x:v>
       </x:c>
       <x:c r="D101" t="str">
         <x:v>Persona</x:v>
@@ -1692,13 +1683,13 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="str">
-        <x:v>70000101</x:v>
+        <x:v>90000022</x:v>
       </x:c>
       <x:c r="B102" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C102" t="str">
-        <x:v>Cliente Persona 101</x:v>
+        <x:v>Lucía Rodríguez Valdez</x:v>
       </x:c>
       <x:c r="D102" t="str">
         <x:v>Persona</x:v>
@@ -1706,13 +1697,13 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="str">
-        <x:v>70000102</x:v>
+        <x:v>90000148</x:v>
       </x:c>
       <x:c r="B103" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C103" t="str">
-        <x:v>Cliente Persona 102</x:v>
+        <x:v>Sofía Espinoza Flores</x:v>
       </x:c>
       <x:c r="D103" t="str">
         <x:v>Persona</x:v>
@@ -1720,13 +1711,13 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="str">
-        <x:v>70000103</x:v>
+        <x:v>90000025</x:v>
       </x:c>
       <x:c r="B104" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C104" t="str">
-        <x:v>Cliente Persona 103</x:v>
+        <x:v>Camila Cárdenas Aguilar</x:v>
       </x:c>
       <x:c r="D104" t="str">
         <x:v>Persona</x:v>
@@ -1734,27 +1725,27 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="str">
-        <x:v>70000104</x:v>
+        <x:v>20990000067</x:v>
       </x:c>
       <x:c r="B105" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C105" t="str">
-        <x:v>Cliente Persona 104</x:v>
+        <x:v>Corporación Sol del Norte 67 S.A.C.</x:v>
       </x:c>
       <x:c r="D105" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="str">
-        <x:v>70000105</x:v>
+        <x:v>90000166</x:v>
       </x:c>
       <x:c r="B106" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C106" t="str">
-        <x:v>Cliente Persona 105</x:v>
+        <x:v>Luis Castillo Mendoza</x:v>
       </x:c>
       <x:c r="D106" t="str">
         <x:v>Persona</x:v>
@@ -1762,13 +1753,13 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="str">
-        <x:v>70000106</x:v>
+        <x:v>90000047</x:v>
       </x:c>
       <x:c r="B107" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C107" t="str">
-        <x:v>Cliente Persona 106</x:v>
+        <x:v>Fiorella Quispe Mendoza</x:v>
       </x:c>
       <x:c r="D107" t="str">
         <x:v>Persona</x:v>
@@ -1776,27 +1767,27 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="str">
-        <x:v>70000107</x:v>
+        <x:v>20990000038</x:v>
       </x:c>
       <x:c r="B108" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C108" t="str">
-        <x:v>Cliente Persona 107</x:v>
+        <x:v>Importaciones Progreso 38 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D108" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="str">
-        <x:v>70000108</x:v>
+        <x:v>90000128</x:v>
       </x:c>
       <x:c r="B109" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C109" t="str">
-        <x:v>Cliente Persona 108</x:v>
+        <x:v>Martín Mendoza Aguilar</x:v>
       </x:c>
       <x:c r="D109" t="str">
         <x:v>Persona</x:v>
@@ -1804,13 +1795,13 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="str">
-        <x:v>70000109</x:v>
+        <x:v>90000052</x:v>
       </x:c>
       <x:c r="B110" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C110" t="str">
-        <x:v>Cliente Persona 109</x:v>
+        <x:v>Paola Sánchez Medina</x:v>
       </x:c>
       <x:c r="D110" t="str">
         <x:v>Persona</x:v>
@@ -1818,27 +1809,27 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="str">
-        <x:v>70000110</x:v>
+        <x:v>20990000027</x:v>
       </x:c>
       <x:c r="B111" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C111" t="str">
-        <x:v>Cliente Persona 110</x:v>
+        <x:v>Suministros Pacífico 27 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D111" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="str">
-        <x:v>70000111</x:v>
+        <x:v>90000093</x:v>
       </x:c>
       <x:c r="B112" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C112" t="str">
-        <x:v>Cliente Persona 111</x:v>
+        <x:v>Rosa Aguilar Cueva</x:v>
       </x:c>
       <x:c r="D112" t="str">
         <x:v>Persona</x:v>
@@ -1846,13 +1837,13 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="str">
-        <x:v>70000112</x:v>
+        <x:v>90000054</x:v>
       </x:c>
       <x:c r="B113" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C113" t="str">
-        <x:v>Cliente Persona 112</x:v>
+        <x:v>Martín Aguilar Campos</x:v>
       </x:c>
       <x:c r="D113" t="str">
         <x:v>Persona</x:v>
@@ -1860,13 +1851,13 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="str">
-        <x:v>70000113</x:v>
+        <x:v>90000045</x:v>
       </x:c>
       <x:c r="B114" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C114" t="str">
-        <x:v>Cliente Persona 113</x:v>
+        <x:v>Rosa Vargas Valdez</x:v>
       </x:c>
       <x:c r="D114" t="str">
         <x:v>Persona</x:v>
@@ -1874,13 +1865,13 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="str">
-        <x:v>70000114</x:v>
+        <x:v>90000114</x:v>
       </x:c>
       <x:c r="B115" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C115" t="str">
-        <x:v>Cliente Persona 114</x:v>
+        <x:v>Renzo Cueva Rodríguez</x:v>
       </x:c>
       <x:c r="D115" t="str">
         <x:v>Persona</x:v>
@@ -1888,13 +1879,13 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="str">
-        <x:v>70000115</x:v>
+        <x:v>90000068</x:v>
       </x:c>
       <x:c r="B116" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C116" t="str">
-        <x:v>Cliente Persona 115</x:v>
+        <x:v>Martín Flores Gutiérrez</x:v>
       </x:c>
       <x:c r="D116" t="str">
         <x:v>Persona</x:v>
@@ -1902,13 +1893,13 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="str">
-        <x:v>70000116</x:v>
+        <x:v>90000126</x:v>
       </x:c>
       <x:c r="B117" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C117" t="str">
-        <x:v>Cliente Persona 116</x:v>
+        <x:v>César Campos García</x:v>
       </x:c>
       <x:c r="D117" t="str">
         <x:v>Persona</x:v>
@@ -1916,27 +1907,27 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="str">
-        <x:v>70000117</x:v>
+        <x:v>20990000039</x:v>
       </x:c>
       <x:c r="B118" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C118" t="str">
-        <x:v>Cliente Persona 117</x:v>
+        <x:v>Suministros Horizonte 39 S.R.L.</x:v>
       </x:c>
       <x:c r="D118" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="str">
-        <x:v>70000118</x:v>
+        <x:v>90000035</x:v>
       </x:c>
       <x:c r="B119" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C119" t="str">
-        <x:v>Cliente Persona 118</x:v>
+        <x:v>Carlos Herrera Cueva</x:v>
       </x:c>
       <x:c r="D119" t="str">
         <x:v>Persona</x:v>
@@ -1944,41 +1935,41 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="str">
-        <x:v>70000119</x:v>
+        <x:v>20990000023</x:v>
       </x:c>
       <x:c r="B120" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C120" t="str">
-        <x:v>Cliente Persona 119</x:v>
+        <x:v>Corporación Horizonte 23 S.A.C.</x:v>
       </x:c>
       <x:c r="D120" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="str">
-        <x:v>70000120</x:v>
+        <x:v>20990000065</x:v>
       </x:c>
       <x:c r="B121" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C121" t="str">
-        <x:v>Cliente Persona 120</x:v>
+        <x:v>Corporación Santa Rosa 65 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D121" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="str">
-        <x:v>70000121</x:v>
+        <x:v>90000018</x:v>
       </x:c>
       <x:c r="B122" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C122" t="str">
-        <x:v>Cliente Persona 121</x:v>
+        <x:v>María Rodríguez Herrera</x:v>
       </x:c>
       <x:c r="D122" t="str">
         <x:v>Persona</x:v>
@@ -1986,13 +1977,13 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="str">
-        <x:v>70000122</x:v>
+        <x:v>90000077</x:v>
       </x:c>
       <x:c r="B123" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C123" t="str">
-        <x:v>Cliente Persona 122</x:v>
+        <x:v>Christian Vega Reyes</x:v>
       </x:c>
       <x:c r="D123" t="str">
         <x:v>Persona</x:v>
@@ -2000,27 +1991,27 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="str">
-        <x:v>70000123</x:v>
+        <x:v>20990000054</x:v>
       </x:c>
       <x:c r="B124" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C124" t="str">
-        <x:v>Cliente Persona 123</x:v>
+        <x:v>Grupo Comercial San Marcos 54 S.R.L.</x:v>
       </x:c>
       <x:c r="D124" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="str">
-        <x:v>70000124</x:v>
+        <x:v>90000048</x:v>
       </x:c>
       <x:c r="B125" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C125" t="str">
-        <x:v>Cliente Persona 124</x:v>
+        <x:v>Daniela García Cueva</x:v>
       </x:c>
       <x:c r="D125" t="str">
         <x:v>Persona</x:v>
@@ -2028,13 +2019,13 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" t="str">
-        <x:v>70000125</x:v>
+        <x:v>90000142</x:v>
       </x:c>
       <x:c r="B126" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C126" t="str">
-        <x:v>Cliente Persona 125</x:v>
+        <x:v>Miguel Espinoza García</x:v>
       </x:c>
       <x:c r="D126" t="str">
         <x:v>Persona</x:v>
@@ -2042,13 +2033,13 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="str">
-        <x:v>70000126</x:v>
+        <x:v>90000028</x:v>
       </x:c>
       <x:c r="B127" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C127" t="str">
-        <x:v>Cliente Persona 126</x:v>
+        <x:v>Fiorella Sánchez Ramírez</x:v>
       </x:c>
       <x:c r="D127" t="str">
         <x:v>Persona</x:v>
@@ -2056,41 +2047,41 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="str">
-        <x:v>70000127</x:v>
+        <x:v>20990000008</x:v>
       </x:c>
       <x:c r="B128" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C128" t="str">
-        <x:v>Cliente Persona 127</x:v>
+        <x:v>Servicios Generales Central 08 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D128" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="str">
-        <x:v>70000128</x:v>
+        <x:v>20990000061</x:v>
       </x:c>
       <x:c r="B129" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C129" t="str">
-        <x:v>Cliente Persona 128</x:v>
+        <x:v>Distribuidora Sol del Norte 61 S.A.C.</x:v>
       </x:c>
       <x:c r="D129" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="str">
-        <x:v>70000129</x:v>
+        <x:v>90000125</x:v>
       </x:c>
       <x:c r="B130" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C130" t="str">
-        <x:v>Cliente Persona 129</x:v>
+        <x:v>Gabriela Rodríguez Reyes</x:v>
       </x:c>
       <x:c r="D130" t="str">
         <x:v>Persona</x:v>
@@ -2098,13 +2089,13 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="str">
-        <x:v>70000130</x:v>
+        <x:v>90000156</x:v>
       </x:c>
       <x:c r="B131" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C131" t="str">
-        <x:v>Cliente Persona 130</x:v>
+        <x:v>María Silva Flores</x:v>
       </x:c>
       <x:c r="D131" t="str">
         <x:v>Persona</x:v>
@@ -2112,13 +2103,13 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" t="str">
-        <x:v>70000131</x:v>
+        <x:v>90000167</x:v>
       </x:c>
       <x:c r="B132" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C132" t="str">
-        <x:v>Cliente Persona 131</x:v>
+        <x:v>Luis Torres Navarro</x:v>
       </x:c>
       <x:c r="D132" t="str">
         <x:v>Persona</x:v>
@@ -2126,13 +2117,13 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="str">
-        <x:v>70000132</x:v>
+        <x:v>90000136</x:v>
       </x:c>
       <x:c r="B133" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C133" t="str">
-        <x:v>Cliente Persona 132</x:v>
+        <x:v>Rosa García Mendoza</x:v>
       </x:c>
       <x:c r="D133" t="str">
         <x:v>Persona</x:v>
@@ -2140,13 +2131,13 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="str">
-        <x:v>70000133</x:v>
+        <x:v>90000061</x:v>
       </x:c>
       <x:c r="B134" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C134" t="str">
-        <x:v>Cliente Persona 133</x:v>
+        <x:v>Diego Castillo Castillo</x:v>
       </x:c>
       <x:c r="D134" t="str">
         <x:v>Persona</x:v>
@@ -2154,13 +2145,13 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="str">
-        <x:v>70000134</x:v>
+        <x:v>90000145</x:v>
       </x:c>
       <x:c r="B135" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C135" t="str">
-        <x:v>Cliente Persona 134</x:v>
+        <x:v>Camila Reyes Campos</x:v>
       </x:c>
       <x:c r="D135" t="str">
         <x:v>Persona</x:v>
@@ -2168,13 +2159,13 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" t="str">
-        <x:v>70000135</x:v>
+        <x:v>90000130</x:v>
       </x:c>
       <x:c r="B136" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C136" t="str">
-        <x:v>Cliente Persona 135</x:v>
+        <x:v>José Ramírez López</x:v>
       </x:c>
       <x:c r="D136" t="str">
         <x:v>Persona</x:v>
@@ -2182,13 +2173,13 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="str">
-        <x:v>70000136</x:v>
+        <x:v>90000032</x:v>
       </x:c>
       <x:c r="B137" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C137" t="str">
-        <x:v>Cliente Persona 136</x:v>
+        <x:v>Claudia Valdez Quispe</x:v>
       </x:c>
       <x:c r="D137" t="str">
         <x:v>Persona</x:v>
@@ -2196,13 +2187,13 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="str">
-        <x:v>70000137</x:v>
+        <x:v>90000124</x:v>
       </x:c>
       <x:c r="B138" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C138" t="str">
-        <x:v>Cliente Persona 137</x:v>
+        <x:v>Luis Campos Sánchez</x:v>
       </x:c>
       <x:c r="D138" t="str">
         <x:v>Persona</x:v>
@@ -2210,27 +2201,27 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="str">
-        <x:v>70000138</x:v>
+        <x:v>20990000005</x:v>
       </x:c>
       <x:c r="B139" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C139" t="str">
-        <x:v>Cliente Persona 138</x:v>
+        <x:v>Servicios Generales Futura 05 S.R.L.</x:v>
       </x:c>
       <x:c r="D139" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="str">
-        <x:v>70000139</x:v>
+        <x:v>90000176</x:v>
       </x:c>
       <x:c r="B140" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C140" t="str">
-        <x:v>Cliente Persona 139</x:v>
+        <x:v>Miguel Mendoza Campos</x:v>
       </x:c>
       <x:c r="D140" t="str">
         <x:v>Persona</x:v>
@@ -2238,41 +2229,41 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" t="str">
-        <x:v>70000140</x:v>
+        <x:v>20990000017</x:v>
       </x:c>
       <x:c r="B141" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C141" t="str">
-        <x:v>Cliente Persona 140</x:v>
+        <x:v>Corporación Continental 17 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D141" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" t="str">
-        <x:v>70000141</x:v>
+        <x:v>20990000011</x:v>
       </x:c>
       <x:c r="B142" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C142" t="str">
-        <x:v>Cliente Persona 141</x:v>
+        <x:v>Comercial Los Cedros 11 S.R.L.</x:v>
       </x:c>
       <x:c r="D142" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" t="str">
-        <x:v>70000142</x:v>
+        <x:v>90000170</x:v>
       </x:c>
       <x:c r="B143" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C143" t="str">
-        <x:v>Cliente Persona 142</x:v>
+        <x:v>Christian Mendoza Salazar</x:v>
       </x:c>
       <x:c r="D143" t="str">
         <x:v>Persona</x:v>
@@ -2280,13 +2271,13 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" t="str">
-        <x:v>70000143</x:v>
+        <x:v>90000150</x:v>
       </x:c>
       <x:c r="B144" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C144" t="str">
-        <x:v>Cliente Persona 143</x:v>
+        <x:v>Eduardo Reyes Valdez</x:v>
       </x:c>
       <x:c r="D144" t="str">
         <x:v>Persona</x:v>
@@ -2294,27 +2285,27 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" t="str">
-        <x:v>70000144</x:v>
+        <x:v>20990000031</x:v>
       </x:c>
       <x:c r="B145" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C145" t="str">
-        <x:v>Cliente Persona 144</x:v>
+        <x:v>Suministros Horizonte 31 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D145" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" t="str">
-        <x:v>70000145</x:v>
+        <x:v>90000030</x:v>
       </x:c>
       <x:c r="B146" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C146" t="str">
-        <x:v>Cliente Persona 145</x:v>
+        <x:v>Christian Cárdenas Sánchez</x:v>
       </x:c>
       <x:c r="D146" t="str">
         <x:v>Persona</x:v>
@@ -2322,41 +2313,41 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" t="str">
-        <x:v>70000146</x:v>
+        <x:v>20990000024</x:v>
       </x:c>
       <x:c r="B147" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C147" t="str">
-        <x:v>Cliente Persona 146</x:v>
+        <x:v>Servicios Generales Victoria 24 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D147" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" t="str">
-        <x:v>70000147</x:v>
+        <x:v>20990000014</x:v>
       </x:c>
       <x:c r="B148" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C148" t="str">
-        <x:v>Cliente Persona 147</x:v>
+        <x:v>Representaciones Lima Norte 14 S.R.L.</x:v>
       </x:c>
       <x:c r="D148" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" t="str">
-        <x:v>70000148</x:v>
+        <x:v>90000146</x:v>
       </x:c>
       <x:c r="B149" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C149" t="str">
-        <x:v>Cliente Persona 148</x:v>
+        <x:v>María Mendoza Navarro</x:v>
       </x:c>
       <x:c r="D149" t="str">
         <x:v>Persona</x:v>
@@ -2364,13 +2355,13 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" t="str">
-        <x:v>70000149</x:v>
+        <x:v>90000027</x:v>
       </x:c>
       <x:c r="B150" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C150" t="str">
-        <x:v>Cliente Persona 149</x:v>
+        <x:v>Álvaro García Campos</x:v>
       </x:c>
       <x:c r="D150" t="str">
         <x:v>Persona</x:v>
@@ -2378,13 +2369,13 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" t="str">
-        <x:v>70000150</x:v>
+        <x:v>90000163</x:v>
       </x:c>
       <x:c r="B151" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C151" t="str">
-        <x:v>Cliente Persona 150</x:v>
+        <x:v>Fernando Chávez Espinoza</x:v>
       </x:c>
       <x:c r="D151" t="str">
         <x:v>Persona</x:v>
@@ -2392,13 +2383,13 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" t="str">
-        <x:v>70000151</x:v>
+        <x:v>90000046</x:v>
       </x:c>
       <x:c r="B152" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C152" t="str">
-        <x:v>Cliente Persona 151</x:v>
+        <x:v>Ricardo Espinoza Fernández</x:v>
       </x:c>
       <x:c r="D152" t="str">
         <x:v>Persona</x:v>
@@ -2406,27 +2397,27 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" t="str">
-        <x:v>70000152</x:v>
+        <x:v>20990000041</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>Cliente Persona 152</x:v>
+        <x:v>Corporación Andina 41 S.R.L.</x:v>
       </x:c>
       <x:c r="D153" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" t="str">
-        <x:v>70000153</x:v>
+        <x:v>90000005</x:v>
       </x:c>
       <x:c r="B154" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C154" t="str">
-        <x:v>Cliente Persona 153</x:v>
+        <x:v>Eduardo Cueva Rojas</x:v>
       </x:c>
       <x:c r="D154" t="str">
         <x:v>Persona</x:v>
@@ -2434,13 +2425,13 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" t="str">
-        <x:v>70000154</x:v>
+        <x:v>90000141</x:v>
       </x:c>
       <x:c r="B155" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C155" t="str">
-        <x:v>Cliente Persona 154</x:v>
+        <x:v>Rosa Herrera Ramírez</x:v>
       </x:c>
       <x:c r="D155" t="str">
         <x:v>Persona</x:v>
@@ -2448,13 +2439,13 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" t="str">
-        <x:v>70000155</x:v>
+        <x:v>90000044</x:v>
       </x:c>
       <x:c r="B156" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C156" t="str">
-        <x:v>Cliente Persona 155</x:v>
+        <x:v>Andrea Ramírez Salazar</x:v>
       </x:c>
       <x:c r="D156" t="str">
         <x:v>Persona</x:v>
@@ -2462,13 +2453,13 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" t="str">
-        <x:v>70000156</x:v>
+        <x:v>90000004</x:v>
       </x:c>
       <x:c r="B157" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C157" t="str">
-        <x:v>Cliente Persona 156</x:v>
+        <x:v>Fiorella Castillo Fernández</x:v>
       </x:c>
       <x:c r="D157" t="str">
         <x:v>Persona</x:v>
@@ -2476,13 +2467,13 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" t="str">
-        <x:v>70000157</x:v>
+        <x:v>90000040</x:v>
       </x:c>
       <x:c r="B158" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C158" t="str">
-        <x:v>Cliente Persona 157</x:v>
+        <x:v>Andrea Silva Medina</x:v>
       </x:c>
       <x:c r="D158" t="str">
         <x:v>Persona</x:v>
@@ -2490,13 +2481,13 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" t="str">
-        <x:v>70000158</x:v>
+        <x:v>90000015</x:v>
       </x:c>
       <x:c r="B159" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C159" t="str">
-        <x:v>Cliente Persona 158</x:v>
+        <x:v>Paola Flores Castillo</x:v>
       </x:c>
       <x:c r="D159" t="str">
         <x:v>Persona</x:v>
@@ -2504,55 +2495,55 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" t="str">
-        <x:v>70000159</x:v>
+        <x:v>20990000056</x:v>
       </x:c>
       <x:c r="B160" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C160" t="str">
-        <x:v>Cliente Persona 159</x:v>
+        <x:v>Negocios Victoria 56 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D160" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" t="str">
-        <x:v>70000160</x:v>
+        <x:v>20990000002</x:v>
       </x:c>
       <x:c r="B161" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C161" t="str">
-        <x:v>Cliente Persona 160</x:v>
+        <x:v>Representaciones Lima Norte 02 S.A.C.</x:v>
       </x:c>
       <x:c r="D161" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" t="str">
-        <x:v>70000161</x:v>
+        <x:v>20990000040</x:v>
       </x:c>
       <x:c r="B162" t="str">
-        <x:v>DNI</x:v>
+        <x:v>RUC</x:v>
       </x:c>
       <x:c r="C162" t="str">
-        <x:v>Cliente Persona 161</x:v>
+        <x:v>Representaciones Imperial 40 S.R.L.</x:v>
       </x:c>
       <x:c r="D162" t="str">
-        <x:v>Persona</x:v>
+        <x:v>Empresa</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" t="str">
-        <x:v>70000162</x:v>
+        <x:v>90000169</x:v>
       </x:c>
       <x:c r="B163" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C163" t="str">
-        <x:v>Cliente Persona 162</x:v>
+        <x:v>Jorge Rojas Fernández</x:v>
       </x:c>
       <x:c r="D163" t="str">
         <x:v>Persona</x:v>
@@ -2560,13 +2551,13 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" t="str">
-        <x:v>70000163</x:v>
+        <x:v>90000106</x:v>
       </x:c>
       <x:c r="B164" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C164" t="str">
-        <x:v>Cliente Persona 163</x:v>
+        <x:v>Camila García Mendoza</x:v>
       </x:c>
       <x:c r="D164" t="str">
         <x:v>Persona</x:v>
@@ -2574,13 +2565,13 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" t="str">
-        <x:v>70000164</x:v>
+        <x:v>90000029</x:v>
       </x:c>
       <x:c r="B165" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C165" t="str">
-        <x:v>Cliente Persona 164</x:v>
+        <x:v>Carlos Paredes Valdez</x:v>
       </x:c>
       <x:c r="D165" t="str">
         <x:v>Persona</x:v>
@@ -2588,13 +2579,13 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" t="str">
-        <x:v>70000165</x:v>
+        <x:v>90000014</x:v>
       </x:c>
       <x:c r="B166" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C166" t="str">
-        <x:v>Cliente Persona 165</x:v>
+        <x:v>Ricardo Cueva Ramírez</x:v>
       </x:c>
       <x:c r="D166" t="str">
         <x:v>Persona</x:v>
@@ -2602,13 +2593,13 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" t="str">
-        <x:v>70000166</x:v>
+        <x:v>90000117</x:v>
       </x:c>
       <x:c r="B167" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C167" t="str">
-        <x:v>Cliente Persona 166</x:v>
+        <x:v>Camila Paredes García</x:v>
       </x:c>
       <x:c r="D167" t="str">
         <x:v>Persona</x:v>
@@ -2616,13 +2607,13 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" t="str">
-        <x:v>70000167</x:v>
+        <x:v>90000110</x:v>
       </x:c>
       <x:c r="B168" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C168" t="str">
-        <x:v>Cliente Persona 167</x:v>
+        <x:v>Renzo Paredes Vega</x:v>
       </x:c>
       <x:c r="D168" t="str">
         <x:v>Persona</x:v>
@@ -2630,13 +2621,13 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" t="str">
-        <x:v>70000168</x:v>
+        <x:v>90000155</x:v>
       </x:c>
       <x:c r="B169" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C169" t="str">
-        <x:v>Cliente Persona 168</x:v>
+        <x:v>Ricardo Fernández Silva</x:v>
       </x:c>
       <x:c r="D169" t="str">
         <x:v>Persona</x:v>
@@ -2644,13 +2635,13 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" t="str">
-        <x:v>70000169</x:v>
+        <x:v>90000097</x:v>
       </x:c>
       <x:c r="B170" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C170" t="str">
-        <x:v>Cliente Persona 169</x:v>
+        <x:v>María Espinoza Chávez</x:v>
       </x:c>
       <x:c r="D170" t="str">
         <x:v>Persona</x:v>
@@ -2658,13 +2649,13 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" t="str">
-        <x:v>70000170</x:v>
+        <x:v>90000160</x:v>
       </x:c>
       <x:c r="B171" t="str">
         <x:v>DNI</x:v>
       </x:c>
       <x:c r="C171" t="str">
-        <x:v>Cliente Persona 170</x:v>
+        <x:v>Christian Cueva Rojas</x:v>
       </x:c>
       <x:c r="D171" t="str">
         <x:v>Persona</x:v>
@@ -2672,125 +2663,125 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" t="str">
-        <x:v>20900000001</x:v>
+        <x:v>90000078</x:v>
       </x:c>
       <x:c r="B172" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C172" t="str">
-        <x:v>Librería Empresa 001 S.A.C.</x:v>
+        <x:v>Patricia Sánchez Vega</x:v>
       </x:c>
       <x:c r="D172" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" t="str">
-        <x:v>20900000002</x:v>
+        <x:v>90000010</x:v>
       </x:c>
       <x:c r="B173" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C173" t="str">
-        <x:v>Librería Empresa 002 S.A.C.</x:v>
+        <x:v>María López Medina</x:v>
       </x:c>
       <x:c r="D173" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" t="str">
-        <x:v>20900000003</x:v>
+        <x:v>90000037</x:v>
       </x:c>
       <x:c r="B174" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C174" t="str">
-        <x:v>Librería Empresa 003 S.A.C.</x:v>
+        <x:v>José Silva Ramírez</x:v>
       </x:c>
       <x:c r="D174" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" t="str">
-        <x:v>20900000004</x:v>
+        <x:v>90000105</x:v>
       </x:c>
       <x:c r="B175" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C175" t="str">
-        <x:v>Librería Empresa 004 S.A.C.</x:v>
+        <x:v>Renzo Cueva Reyes</x:v>
       </x:c>
       <x:c r="D175" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" t="str">
-        <x:v>20900000005</x:v>
+        <x:v>90000120</x:v>
       </x:c>
       <x:c r="B176" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C176" t="str">
-        <x:v>Librería Empresa 005 S.A.C.</x:v>
+        <x:v>Carlos Herrera Navarro</x:v>
       </x:c>
       <x:c r="D176" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" t="str">
-        <x:v>20900000006</x:v>
+        <x:v>90000082</x:v>
       </x:c>
       <x:c r="B177" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C177" t="str">
-        <x:v>Librería Empresa 006 S.A.C.</x:v>
+        <x:v>José Mendoza Aguilar</x:v>
       </x:c>
       <x:c r="D177" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" t="str">
-        <x:v>20900000007</x:v>
+        <x:v>90000074</x:v>
       </x:c>
       <x:c r="B178" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C178" t="str">
-        <x:v>Librería Empresa 007 S.A.C.</x:v>
+        <x:v>Daniela Vargas Ramírez</x:v>
       </x:c>
       <x:c r="D178" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" t="str">
-        <x:v>20900000008</x:v>
+        <x:v>90000135</x:v>
       </x:c>
       <x:c r="B179" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C179" t="str">
-        <x:v>Librería Empresa 008 S.A.C.</x:v>
+        <x:v>Claudia Fernández Ramírez</x:v>
       </x:c>
       <x:c r="D179" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" t="str">
-        <x:v>20900000009</x:v>
+        <x:v>20990000070</x:v>
       </x:c>
       <x:c r="B180" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C180" t="str">
-        <x:v>Librería Empresa 009 S.A.C.</x:v>
+        <x:v>Servicios Generales Imperial 70 S.A.C.</x:v>
       </x:c>
       <x:c r="D180" t="str">
         <x:v>Empresa</x:v>
@@ -2798,27 +2789,27 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" t="str">
-        <x:v>20900000010</x:v>
+        <x:v>90000119</x:v>
       </x:c>
       <x:c r="B181" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C181" t="str">
-        <x:v>Librería Empresa 010 S.A.C.</x:v>
+        <x:v>Alejandra Rojas Paredes</x:v>
       </x:c>
       <x:c r="D181" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" t="str">
-        <x:v>20900000011</x:v>
+        <x:v>20990000007</x:v>
       </x:c>
       <x:c r="B182" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C182" t="str">
-        <x:v>Librería Empresa 011 S.A.C.</x:v>
+        <x:v>Suministros Alianza 07 S.R.L.</x:v>
       </x:c>
       <x:c r="D182" t="str">
         <x:v>Empresa</x:v>
@@ -2826,55 +2817,55 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" t="str">
-        <x:v>20900000012</x:v>
+        <x:v>90000051</x:v>
       </x:c>
       <x:c r="B183" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C183" t="str">
-        <x:v>Librería Empresa 012 S.A.C.</x:v>
+        <x:v>Jorge Huamán Vargas</x:v>
       </x:c>
       <x:c r="D183" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" t="str">
-        <x:v>20900000013</x:v>
+        <x:v>90000079</x:v>
       </x:c>
       <x:c r="B184" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C184" t="str">
-        <x:v>Librería Empresa 013 S.A.C.</x:v>
+        <x:v>Luis Torres Cueva</x:v>
       </x:c>
       <x:c r="D184" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" t="str">
-        <x:v>20900000014</x:v>
+        <x:v>90000069</x:v>
       </x:c>
       <x:c r="B185" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C185" t="str">
-        <x:v>Librería Empresa 014 S.A.C.</x:v>
+        <x:v>Lucía Aguilar Rodríguez</x:v>
       </x:c>
       <x:c r="D185" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" t="str">
-        <x:v>20900000015</x:v>
+        <x:v>20990000022</x:v>
       </x:c>
       <x:c r="B186" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C186" t="str">
-        <x:v>Librería Empresa 015 S.A.C.</x:v>
+        <x:v>Inversiones Atenea 22 S.R.L.</x:v>
       </x:c>
       <x:c r="D186" t="str">
         <x:v>Empresa</x:v>
@@ -2882,13 +2873,13 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" t="str">
-        <x:v>20900000016</x:v>
+        <x:v>20990000048</x:v>
       </x:c>
       <x:c r="B187" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C187" t="str">
-        <x:v>Librería Empresa 016 S.A.C.</x:v>
+        <x:v>Representaciones San Marcos 48 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D187" t="str">
         <x:v>Empresa</x:v>
@@ -2896,55 +2887,55 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" t="str">
-        <x:v>20900000017</x:v>
+        <x:v>90000065</x:v>
       </x:c>
       <x:c r="B188" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C188" t="str">
-        <x:v>Librería Empresa 017 S.A.C.</x:v>
+        <x:v>Fiorella López Fernández</x:v>
       </x:c>
       <x:c r="D188" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" t="str">
-        <x:v>20900000018</x:v>
+        <x:v>90000023</x:v>
       </x:c>
       <x:c r="B189" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C189" t="str">
-        <x:v>Librería Empresa 018 S.A.C.</x:v>
+        <x:v>Diego Medina Gutiérrez</x:v>
       </x:c>
       <x:c r="D189" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" t="str">
-        <x:v>20900000019</x:v>
+        <x:v>90000139</x:v>
       </x:c>
       <x:c r="B190" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C190" t="str">
-        <x:v>Librería Empresa 019 S.A.C.</x:v>
+        <x:v>Renzo Silva Reyes</x:v>
       </x:c>
       <x:c r="D190" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" t="str">
-        <x:v>20900000020</x:v>
+        <x:v>20990000013</x:v>
       </x:c>
       <x:c r="B191" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C191" t="str">
-        <x:v>Librería Empresa 020 S.A.C.</x:v>
+        <x:v>Comercial Universal 13 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D191" t="str">
         <x:v>Empresa</x:v>
@@ -2952,27 +2943,27 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" t="str">
-        <x:v>20900000021</x:v>
+        <x:v>90000152</x:v>
       </x:c>
       <x:c r="B192" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C192" t="str">
-        <x:v>Librería Empresa 021 S.A.C.</x:v>
+        <x:v>Ricardo Salazar Flores</x:v>
       </x:c>
       <x:c r="D192" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" t="str">
-        <x:v>20900000022</x:v>
+        <x:v>20990000034</x:v>
       </x:c>
       <x:c r="B193" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C193" t="str">
-        <x:v>Librería Empresa 022 S.A.C.</x:v>
+        <x:v>Distribuidora Imperial 34 S.R.L.</x:v>
       </x:c>
       <x:c r="D193" t="str">
         <x:v>Empresa</x:v>
@@ -2980,41 +2971,41 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" t="str">
-        <x:v>20900000023</x:v>
+        <x:v>90000094</x:v>
       </x:c>
       <x:c r="B194" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C194" t="str">
-        <x:v>Librería Empresa 023 S.A.C.</x:v>
+        <x:v>Camila Rojas López</x:v>
       </x:c>
       <x:c r="D194" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" t="str">
-        <x:v>20900000024</x:v>
+        <x:v>90000086</x:v>
       </x:c>
       <x:c r="B195" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C195" t="str">
-        <x:v>Librería Empresa 024 S.A.C.</x:v>
+        <x:v>María Salazar Quispe</x:v>
       </x:c>
       <x:c r="D195" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" t="str">
-        <x:v>20900000025</x:v>
+        <x:v>20990000051</x:v>
       </x:c>
       <x:c r="B196" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C196" t="str">
-        <x:v>Librería Empresa 025 S.A.C.</x:v>
+        <x:v>Corporación Atenea 51 S.R.L.</x:v>
       </x:c>
       <x:c r="D196" t="str">
         <x:v>Empresa</x:v>
@@ -3022,41 +3013,41 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" t="str">
-        <x:v>20900000026</x:v>
+        <x:v>90000083</x:v>
       </x:c>
       <x:c r="B197" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C197" t="str">
-        <x:v>Librería Empresa 026 S.A.C.</x:v>
+        <x:v>Carlos Sánchez García</x:v>
       </x:c>
       <x:c r="D197" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" t="str">
-        <x:v>20900000027</x:v>
+        <x:v>90000085</x:v>
       </x:c>
       <x:c r="B198" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C198" t="str">
-        <x:v>Librería Empresa 027 S.A.C.</x:v>
+        <x:v>Claudia Huamán García</x:v>
       </x:c>
       <x:c r="D198" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" t="str">
-        <x:v>20900000028</x:v>
+        <x:v>20990000069</x:v>
       </x:c>
       <x:c r="B199" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C199" t="str">
-        <x:v>Librería Empresa 028 S.A.C.</x:v>
+        <x:v>Negocios El Dorado 69 S.R.L.</x:v>
       </x:c>
       <x:c r="D199" t="str">
         <x:v>Empresa</x:v>
@@ -3064,13 +3055,13 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" t="str">
-        <x:v>20900000029</x:v>
+        <x:v>20990000053</x:v>
       </x:c>
       <x:c r="B200" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C200" t="str">
-        <x:v>Librería Empresa 029 S.A.C.</x:v>
+        <x:v>Negocios Nova 53 S.A.C.</x:v>
       </x:c>
       <x:c r="D200" t="str">
         <x:v>Empresa</x:v>
@@ -3078,41 +3069,41 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" t="str">
-        <x:v>20900000030</x:v>
+        <x:v>90000009</x:v>
       </x:c>
       <x:c r="B201" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C201" t="str">
-        <x:v>Librería Empresa 030 S.A.C.</x:v>
+        <x:v>Martín Rodríguez Fernández</x:v>
       </x:c>
       <x:c r="D201" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" t="str">
-        <x:v>20900000031</x:v>
+        <x:v>90000072</x:v>
       </x:c>
       <x:c r="B202" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C202" t="str">
-        <x:v>Librería Empresa 031 S.A.C.</x:v>
+        <x:v>José Silva Aguilar</x:v>
       </x:c>
       <x:c r="D202" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" t="str">
-        <x:v>20900000032</x:v>
+        <x:v>20990000045</x:v>
       </x:c>
       <x:c r="B203" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C203" t="str">
-        <x:v>Librería Empresa 032 S.A.C.</x:v>
+        <x:v>Inversiones San Marcos 45 S.A.C.</x:v>
       </x:c>
       <x:c r="D203" t="str">
         <x:v>Empresa</x:v>
@@ -3120,13 +3111,13 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" t="str">
-        <x:v>20900000033</x:v>
+        <x:v>20990000018</x:v>
       </x:c>
       <x:c r="B204" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C204" t="str">
-        <x:v>Librería Empresa 033 S.A.C.</x:v>
+        <x:v>Servicios Generales Los Cedros 18 S.R.L.</x:v>
       </x:c>
       <x:c r="D204" t="str">
         <x:v>Empresa</x:v>
@@ -3134,13 +3125,13 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" t="str">
-        <x:v>20900000034</x:v>
+        <x:v>20990000057</x:v>
       </x:c>
       <x:c r="B205" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C205" t="str">
-        <x:v>Librería Empresa 034 S.A.C.</x:v>
+        <x:v>Corporación Lima Norte 57 S.A.C.</x:v>
       </x:c>
       <x:c r="D205" t="str">
         <x:v>Empresa</x:v>
@@ -3148,13 +3139,13 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" t="str">
-        <x:v>20900000035</x:v>
+        <x:v>20990000026</x:v>
       </x:c>
       <x:c r="B206" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C206" t="str">
-        <x:v>Librería Empresa 035 S.A.C.</x:v>
+        <x:v>Representaciones Santa Rosa 26 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D206" t="str">
         <x:v>Empresa</x:v>
@@ -3162,97 +3153,97 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" t="str">
-        <x:v>20900000036</x:v>
+        <x:v>90000101</x:v>
       </x:c>
       <x:c r="B207" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C207" t="str">
-        <x:v>Librería Empresa 036 S.A.C.</x:v>
+        <x:v>Christian Huamán Rojas</x:v>
       </x:c>
       <x:c r="D207" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" t="str">
-        <x:v>20900000037</x:v>
+        <x:v>90000144</x:v>
       </x:c>
       <x:c r="B208" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C208" t="str">
-        <x:v>Librería Empresa 037 S.A.C.</x:v>
+        <x:v>Alejandra Chávez Aguilar</x:v>
       </x:c>
       <x:c r="D208" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" t="str">
-        <x:v>20900000038</x:v>
+        <x:v>90000165</x:v>
       </x:c>
       <x:c r="B209" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Librería Empresa 038 S.A.C.</x:v>
+        <x:v>Valeria Cueva Campos</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" t="str">
-        <x:v>20900000039</x:v>
+        <x:v>90000058</x:v>
       </x:c>
       <x:c r="B210" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Librería Empresa 039 S.A.C.</x:v>
+        <x:v>María Reyes Paredes</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" t="str">
-        <x:v>20900000040</x:v>
+        <x:v>90000031</x:v>
       </x:c>
       <x:c r="B211" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Librería Empresa 040 S.A.C.</x:v>
+        <x:v>Martín Ramírez Cueva</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" t="str">
-        <x:v>20900000041</x:v>
+        <x:v>90000055</x:v>
       </x:c>
       <x:c r="B212" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Librería Empresa 041 S.A.C.</x:v>
+        <x:v>Patricia Vega Fernández</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" t="str">
-        <x:v>20900000042</x:v>
+        <x:v>20990000032</x:v>
       </x:c>
       <x:c r="B213" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Librería Empresa 042 S.A.C.</x:v>
+        <x:v>Inversiones Andina 32 S.A.C.</x:v>
       </x:c>
       <x:c r="D213" t="str">
         <x:v>Empresa</x:v>
@@ -3260,13 +3251,13 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" t="str">
-        <x:v>20900000043</x:v>
+        <x:v>20990000036</x:v>
       </x:c>
       <x:c r="B214" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>Librería Empresa 043 S.A.C.</x:v>
+        <x:v>Corporación Futura 36 S.R.L.</x:v>
       </x:c>
       <x:c r="D214" t="str">
         <x:v>Empresa</x:v>
@@ -3274,13 +3265,13 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" t="str">
-        <x:v>20900000044</x:v>
+        <x:v>20990000063</x:v>
       </x:c>
       <x:c r="B215" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Librería Empresa 044 S.A.C.</x:v>
+        <x:v>Distribuidora Sol del Norte 63 S.A.C.</x:v>
       </x:c>
       <x:c r="D215" t="str">
         <x:v>Empresa</x:v>
@@ -3288,55 +3279,55 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" t="str">
-        <x:v>20900000045</x:v>
+        <x:v>90000084</x:v>
       </x:c>
       <x:c r="B216" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C216" t="str">
-        <x:v>Librería Empresa 045 S.A.C.</x:v>
+        <x:v>Luis Gutiérrez García</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" t="str">
-        <x:v>20900000046</x:v>
+        <x:v>90000112</x:v>
       </x:c>
       <x:c r="B217" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C217" t="str">
-        <x:v>Librería Empresa 046 S.A.C.</x:v>
+        <x:v>Daniela Valdez Espinoza</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" t="str">
-        <x:v>20900000047</x:v>
+        <x:v>90000099</x:v>
       </x:c>
       <x:c r="B218" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C218" t="str">
-        <x:v>Librería Empresa 047 S.A.C.</x:v>
+        <x:v>Valeria Aguilar Sánchez</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" t="str">
-        <x:v>20900000048</x:v>
+        <x:v>20990000042</x:v>
       </x:c>
       <x:c r="B219" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C219" t="str">
-        <x:v>Librería Empresa 048 S.A.C.</x:v>
+        <x:v>Servicios Generales San Marcos 42 S.A.C.</x:v>
       </x:c>
       <x:c r="D219" t="str">
         <x:v>Empresa</x:v>
@@ -3344,13 +3335,13 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" t="str">
-        <x:v>20900000049</x:v>
+        <x:v>20990000035</x:v>
       </x:c>
       <x:c r="B220" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C220" t="str">
-        <x:v>Librería Empresa 049 S.A.C.</x:v>
+        <x:v>Comercial Central 35 S.A.C.</x:v>
       </x:c>
       <x:c r="D220" t="str">
         <x:v>Empresa</x:v>
@@ -3358,83 +3349,83 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" t="str">
-        <x:v>20900000050</x:v>
+        <x:v>90000062</x:v>
       </x:c>
       <x:c r="B221" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C221" t="str">
-        <x:v>Librería Empresa 050 S.A.C.</x:v>
+        <x:v>Carlos Valdez García</x:v>
       </x:c>
       <x:c r="D221" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" t="str">
-        <x:v>20900000051</x:v>
+        <x:v>90000012</x:v>
       </x:c>
       <x:c r="B222" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C222" t="str">
-        <x:v>Librería Empresa 051 S.A.C.</x:v>
+        <x:v>Álvaro Sánchez Cueva</x:v>
       </x:c>
       <x:c r="D222" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" t="str">
-        <x:v>20900000052</x:v>
+        <x:v>90000143</x:v>
       </x:c>
       <x:c r="B223" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C223" t="str">
-        <x:v>Librería Empresa 052 S.A.C.</x:v>
+        <x:v>Alejandra Rojas Fernández</x:v>
       </x:c>
       <x:c r="D223" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" t="str">
-        <x:v>20900000053</x:v>
+        <x:v>90000113</x:v>
       </x:c>
       <x:c r="B224" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C224" t="str">
-        <x:v>Librería Empresa 053 S.A.C.</x:v>
+        <x:v>Gabriela Quispe Torres</x:v>
       </x:c>
       <x:c r="D224" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" t="str">
-        <x:v>20900000054</x:v>
+        <x:v>90000067</x:v>
       </x:c>
       <x:c r="B225" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C225" t="str">
-        <x:v>Librería Empresa 054 S.A.C.</x:v>
+        <x:v>Miguel Medina Cueva</x:v>
       </x:c>
       <x:c r="D225" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" t="str">
-        <x:v>20900000055</x:v>
+        <x:v>20990000003</x:v>
       </x:c>
       <x:c r="B226" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C226" t="str">
-        <x:v>Librería Empresa 055 S.A.C.</x:v>
+        <x:v>Negocios Universal 03 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D226" t="str">
         <x:v>Empresa</x:v>
@@ -3442,83 +3433,83 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" t="str">
-        <x:v>20900000056</x:v>
+        <x:v>90000080</x:v>
       </x:c>
       <x:c r="B227" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C227" t="str">
-        <x:v>Librería Empresa 056 S.A.C.</x:v>
+        <x:v>Renzo López Navarro</x:v>
       </x:c>
       <x:c r="D227" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" t="str">
-        <x:v>20900000057</x:v>
+        <x:v>90000096</x:v>
       </x:c>
       <x:c r="B228" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C228" t="str">
-        <x:v>Librería Empresa 057 S.A.C.</x:v>
+        <x:v>Luis Reyes Rojas</x:v>
       </x:c>
       <x:c r="D228" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" t="str">
-        <x:v>20900000058</x:v>
+        <x:v>90000162</x:v>
       </x:c>
       <x:c r="B229" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C229" t="str">
-        <x:v>Librería Empresa 058 S.A.C.</x:v>
+        <x:v>Miguel Reyes Rojas</x:v>
       </x:c>
       <x:c r="D229" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" t="str">
-        <x:v>20900000059</x:v>
+        <x:v>90000087</x:v>
       </x:c>
       <x:c r="B230" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C230" t="str">
-        <x:v>Librería Empresa 059 S.A.C.</x:v>
+        <x:v>Alejandra Fernández Ramírez</x:v>
       </x:c>
       <x:c r="D230" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" t="str">
-        <x:v>20900000060</x:v>
+        <x:v>90000177</x:v>
       </x:c>
       <x:c r="B231" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C231" t="str">
-        <x:v>Librería Empresa 060 S.A.C.</x:v>
+        <x:v>Fernando Herrera López</x:v>
       </x:c>
       <x:c r="D231" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" t="str">
-        <x:v>20900000061</x:v>
+        <x:v>20990000059</x:v>
       </x:c>
       <x:c r="B232" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C232" t="str">
-        <x:v>Librería Empresa 061 S.A.C.</x:v>
+        <x:v>Grupo Comercial Universal 59 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D232" t="str">
         <x:v>Empresa</x:v>
@@ -3526,125 +3517,125 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" t="str">
-        <x:v>20900000062</x:v>
+        <x:v>90000095</x:v>
       </x:c>
       <x:c r="B233" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C233" t="str">
-        <x:v>Librería Empresa 062 S.A.C.</x:v>
+        <x:v>María Fernández López</x:v>
       </x:c>
       <x:c r="D233" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" t="str">
-        <x:v>20900000063</x:v>
+        <x:v>90000091</x:v>
       </x:c>
       <x:c r="B234" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C234" t="str">
-        <x:v>Librería Empresa 063 S.A.C.</x:v>
+        <x:v>Natalia Valdez Quispe</x:v>
       </x:c>
       <x:c r="D234" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" t="str">
-        <x:v>20900000064</x:v>
+        <x:v>90000007</x:v>
       </x:c>
       <x:c r="B235" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C235" t="str">
-        <x:v>Librería Empresa 064 S.A.C.</x:v>
+        <x:v>Diego García Cueva</x:v>
       </x:c>
       <x:c r="D235" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" t="str">
-        <x:v>20900000065</x:v>
+        <x:v>90000088</x:v>
       </x:c>
       <x:c r="B236" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C236" t="str">
-        <x:v>Librería Empresa 065 S.A.C.</x:v>
+        <x:v>Andrea Castillo Vargas</x:v>
       </x:c>
       <x:c r="D236" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" t="str">
-        <x:v>20900000066</x:v>
+        <x:v>90000003</x:v>
       </x:c>
       <x:c r="B237" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C237" t="str">
-        <x:v>Librería Empresa 066 S.A.C.</x:v>
+        <x:v>Gabriela Valdez Espinoza</x:v>
       </x:c>
       <x:c r="D237" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" t="str">
-        <x:v>20900000067</x:v>
+        <x:v>90000092</x:v>
       </x:c>
       <x:c r="B238" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C238" t="str">
-        <x:v>Librería Empresa 067 S.A.C.</x:v>
+        <x:v>César Navarro Navarro</x:v>
       </x:c>
       <x:c r="D238" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
       <x:c r="A239" t="str">
-        <x:v>20900000068</x:v>
+        <x:v>90000075</x:v>
       </x:c>
       <x:c r="B239" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C239" t="str">
-        <x:v>Librería Empresa 068 S.A.C.</x:v>
+        <x:v>José Quispe García</x:v>
       </x:c>
       <x:c r="D239" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" t="str">
-        <x:v>20900000069</x:v>
+        <x:v>90000073</x:v>
       </x:c>
       <x:c r="B240" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C240" t="str">
-        <x:v>Librería Empresa 069 S.A.C.</x:v>
+        <x:v>Daniela Vargas Huamán</x:v>
       </x:c>
       <x:c r="D240" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
       <x:c r="A241" t="str">
-        <x:v>20900000070</x:v>
+        <x:v>20990000068</x:v>
       </x:c>
       <x:c r="B241" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C241" t="str">
-        <x:v>Librería Empresa 070 S.A.C.</x:v>
+        <x:v>Representaciones Los Cedros 68 S.A.C.</x:v>
       </x:c>
       <x:c r="D241" t="str">
         <x:v>Empresa</x:v>
@@ -3652,83 +3643,83 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" t="str">
-        <x:v>20900000071</x:v>
+        <x:v>90000116</x:v>
       </x:c>
       <x:c r="B242" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C242" t="str">
-        <x:v>Librería Empresa 071 S.A.C.</x:v>
+        <x:v>Renzo Paredes Castillo</x:v>
       </x:c>
       <x:c r="D242" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" t="str">
-        <x:v>20900000072</x:v>
+        <x:v>90000109</x:v>
       </x:c>
       <x:c r="B243" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C243" t="str">
-        <x:v>Librería Empresa 072 S.A.C.</x:v>
+        <x:v>Natalia Torres Paredes</x:v>
       </x:c>
       <x:c r="D243" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" t="str">
-        <x:v>20900000073</x:v>
+        <x:v>90000140</x:v>
       </x:c>
       <x:c r="B244" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C244" t="str">
-        <x:v>Librería Empresa 073 S.A.C.</x:v>
+        <x:v>Eduardo Cárdenas Quispe</x:v>
       </x:c>
       <x:c r="D244" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" t="str">
-        <x:v>20900000074</x:v>
+        <x:v>90000070</x:v>
       </x:c>
       <x:c r="B245" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C245" t="str">
-        <x:v>Librería Empresa 074 S.A.C.</x:v>
+        <x:v>Alejandra Castillo Cueva</x:v>
       </x:c>
       <x:c r="D245" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
       <x:c r="A246" t="str">
-        <x:v>20900000075</x:v>
+        <x:v>90000016</x:v>
       </x:c>
       <x:c r="B246" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C246" t="str">
-        <x:v>Librería Empresa 075 S.A.C.</x:v>
+        <x:v>Fernando Torres Silva</x:v>
       </x:c>
       <x:c r="D246" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
       <x:c r="A247" t="str">
-        <x:v>20900000076</x:v>
+        <x:v>20990000060</x:v>
       </x:c>
       <x:c r="B247" t="str">
         <x:v>RUC</x:v>
       </x:c>
       <x:c r="C247" t="str">
-        <x:v>Librería Empresa 076 S.A.C.</x:v>
+        <x:v>Representaciones Futura 60 E.I.R.L.</x:v>
       </x:c>
       <x:c r="D247" t="str">
         <x:v>Empresa</x:v>
@@ -3736,64 +3727,61 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" t="str">
-        <x:v>20900000077</x:v>
+        <x:v>90000164</x:v>
       </x:c>
       <x:c r="B248" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C248" t="str">
-        <x:v>Librería Empresa 077 S.A.C.</x:v>
+        <x:v>Diego Silva Silva</x:v>
       </x:c>
       <x:c r="D248" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" t="str">
-        <x:v>20900000078</x:v>
+        <x:v>90000121</x:v>
       </x:c>
       <x:c r="B249" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C249" t="str">
-        <x:v>Librería Empresa 078 S.A.C.</x:v>
+        <x:v>César Mendoza Gutiérrez</x:v>
       </x:c>
       <x:c r="D249" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
       <x:c r="A250" t="str">
-        <x:v>20900000079</x:v>
+        <x:v>90000151</x:v>
       </x:c>
       <x:c r="B250" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C250" t="str">
-        <x:v>Librería Empresa 079 S.A.C.</x:v>
+        <x:v>Miguel Valdez Medina</x:v>
       </x:c>
       <x:c r="D250" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" t="str">
-        <x:v>20900000080</x:v>
+        <x:v>90000103</x:v>
       </x:c>
       <x:c r="B251" t="str">
-        <x:v>RUC</x:v>
+        <x:v>DNI</x:v>
       </x:c>
       <x:c r="C251" t="str">
-        <x:v>Librería Empresa 080 S.A.C.</x:v>
+        <x:v>Renzo Valdez Salazar</x:v>
       </x:c>
       <x:c r="D251" t="str">
-        <x:v>Empresa</x:v>
+        <x:v>Persona</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63659fc1c91472a"/>
-  </x:tableParts>
 </x:worksheet>
 </file>